--- a/artfynd/A 23777-2025 artfynd.xlsx
+++ b/artfynd/A 23777-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125221021</v>
       </c>
       <c r="B2" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 23777-2025 artfynd.xlsx
+++ b/artfynd/A 23777-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125221021</v>
       </c>
       <c r="B2" t="n">
-        <v>98332</v>
+        <v>98334</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 23777-2025 artfynd.xlsx
+++ b/artfynd/A 23777-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125221021</v>
       </c>
       <c r="B2" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 23777-2025 artfynd.xlsx
+++ b/artfynd/A 23777-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125221021</v>
       </c>
       <c r="B2" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 23777-2025 artfynd.xlsx
+++ b/artfynd/A 23777-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125221021</v>
       </c>
       <c r="B2" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 23777-2025 artfynd.xlsx
+++ b/artfynd/A 23777-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125221021</v>
       </c>
       <c r="B2" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 23777-2025 artfynd.xlsx
+++ b/artfynd/A 23777-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125221021</v>
       </c>
       <c r="B2" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 23777-2025 artfynd.xlsx
+++ b/artfynd/A 23777-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125221021</v>
       </c>
       <c r="B2" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 23777-2025 artfynd.xlsx
+++ b/artfynd/A 23777-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125221021</v>
       </c>
       <c r="B2" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 23777-2025 artfynd.xlsx
+++ b/artfynd/A 23777-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125221021</v>
       </c>
       <c r="B2" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 23777-2025 artfynd.xlsx
+++ b/artfynd/A 23777-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>125221021</v>
       </c>
       <c r="B2" t="n">
-        <v>98361</v>
+        <v>99118</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,6 +784,228 @@
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>125221023</v>
+      </c>
+      <c r="B3" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Laforsen, Hls</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>521176</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6861034</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-04-29</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-04-29</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>125221026</v>
+      </c>
+      <c r="B4" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Laforsen, Hls</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>521188</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6861071</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-04-29</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-04-29</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 23777-2025 artfynd.xlsx
+++ b/artfynd/A 23777-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -783,6 +788,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125221021</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -894,6 +904,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125221023</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1005,8 +1020,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125221026</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>